--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104611_W17.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104611_W17.xlsx
@@ -565,58 +565,58 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.8711</v>
+        <v>5.5288</v>
       </c>
       <c r="E2" t="n">
-        <v>6.461</v>
+        <v>5.4019</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4102</v>
+        <v>0.1269</v>
       </c>
       <c r="G2" t="n">
-        <v>2.2982</v>
+        <v>2.2978</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.7245</v>
+        <v>-0.7184</v>
       </c>
       <c r="I2" t="n">
-        <v>3.0227</v>
+        <v>3.0162</v>
       </c>
       <c r="J2" t="n">
-        <v>4.7279</v>
+        <v>4.7053</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2526</v>
+        <v>0.2446</v>
       </c>
       <c r="L2" t="n">
-        <v>4.4753</v>
+        <v>4.4608</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.4298</v>
+        <v>-2.4075</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.9771</v>
+        <v>-0.9629</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.4526</v>
+        <v>-1.4446</v>
       </c>
       <c r="P2" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S2" t="n">
-        <v>2.7583</v>
+        <v>1.4099</v>
       </c>
       <c r="T2" t="n">
-        <v>1.733</v>
+        <v>0.6965</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0253</v>
+        <v>0.7134</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6996</v>
+        <v>0.5508</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1232</v>
+        <v>2.1278</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.4236</v>
+        <v>-1.577</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.6043</v>
+        <v>-1.5906</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4241</v>
+        <v>0.4305</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.0284</v>
+        <v>-2.0211</v>
       </c>
       <c r="J3" t="n">
-        <v>2.1499</v>
+        <v>2.1352</v>
       </c>
       <c r="K3" t="n">
-        <v>2.078</v>
+        <v>2.0684</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.0668</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.7542</v>
+        <v>-3.7258</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.6539</v>
+        <v>-1.638</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.1003</v>
+        <v>-2.0879</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3285</v>
+        <v>0.1626</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1875</v>
+        <v>-0.1652</v>
       </c>
       <c r="U3" t="n">
-        <v>0.516</v>
+        <v>0.3278</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6805</v>
+        <v>0.3857</v>
       </c>
       <c r="E4" t="n">
-        <v>1.359</v>
+        <v>1.239</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6785</v>
+        <v>-0.8532999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.4676</v>
+        <v>-0.4598</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3001</v>
+        <v>0.3042</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7675999999999999</v>
+        <v>-0.764</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9205</v>
+        <v>0.9163</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8832</v>
+        <v>0.8791</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.388</v>
+        <v>-1.3761</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5831</v>
+        <v>-0.5749</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.805</v>
+        <v>-0.8012</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6944</v>
+        <v>0.3902</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4386</v>
+        <v>0.3227</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2559</v>
+        <v>0.0675</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0125</v>
+        <v>0.1829</v>
       </c>
       <c r="E5" t="n">
-        <v>3.6883</v>
+        <v>3.911</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.7008</v>
+        <v>-3.728</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1847</v>
+        <v>1.1781</v>
       </c>
       <c r="H5" t="n">
-        <v>2.2109</v>
+        <v>2.1951</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.0262</v>
+        <v>-1.017</v>
       </c>
       <c r="J5" t="n">
-        <v>4.2035</v>
+        <v>4.1724</v>
       </c>
       <c r="K5" t="n">
-        <v>3.3452</v>
+        <v>3.316</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8583</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.0188</v>
+        <v>-2.9943</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.1344</v>
+        <v>-1.1209</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.8844</v>
+        <v>-1.8734</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R5" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5831</v>
+        <v>-0.3902</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8347</v>
+        <v>-0.5786</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2516</v>
+        <v>0.1884</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.7483</v>
+        <v>-1.7432</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.2946</v>
+        <v>-2.2879</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. BRIZUELA</t>
+          <t>M. CALE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.3417</v>
+        <v>-0.8051</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.8727</v>
+        <v>0.8391999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.531</v>
+        <v>-1.6442</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4945</v>
+        <v>0.0485</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1905</v>
+        <v>0.6545</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6850000000000001</v>
+        <v>-0.6061</v>
       </c>
       <c r="J6" t="n">
-        <v>1.179</v>
+        <v>0.9508</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0622</v>
+        <v>0.9136</v>
       </c>
       <c r="L6" t="n">
-        <v>1.1168</v>
+        <v>0.0372</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6844</v>
+        <v>-0.9023</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2526</v>
+        <v>-0.259</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4318</v>
+        <v>-0.6433</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.5878</v>
+        <v>0.4553</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.4952</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9073</v>
+        <v>0.4553</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1391</v>
+        <v>-0.0615</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5565</v>
+        <v>-0.1116</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4174</v>
+        <v>0.0501</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1093</v>
+        <v>-1.2472</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1093</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. CALE</t>
+          <t>D. BRIZUELA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.3467</v>
+        <v>-1.0233</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5377</v>
+        <v>-1.5696</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.8844</v>
+        <v>0.5463</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0389</v>
+        <v>0.491</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6492</v>
+        <v>-0.1896</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6104000000000001</v>
+        <v>0.6806</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9550999999999999</v>
+        <v>1.1644</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9177999999999999</v>
+        <v>0.055</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0373</v>
+        <v>1.1094</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9162</v>
+        <v>-0.6734</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2685</v>
+        <v>-0.2446</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.4289</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4537</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.5039</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4537</v>
+        <v>0.9105</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5858</v>
+        <v>0.1881</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4174</v>
+        <v>-0.2301</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1685</v>
+        <v>0.4182</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2534</v>
+        <v>-0.1089</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2534</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.032</v>
+        <v>-1.0978</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.1004</v>
+        <v>-1.4741</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0684</v>
+        <v>0.3764</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1697</v>
+        <v>-0.1886</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7287</v>
+        <v>0.7267</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8984</v>
+        <v>-0.9154</v>
       </c>
       <c r="J8" t="n">
-        <v>1.3406</v>
+        <v>1.3018</v>
       </c>
       <c r="K8" t="n">
-        <v>1.6899</v>
+        <v>1.6752</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.3494</v>
+        <v>-0.3735</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.5103</v>
+        <v>-1.4904</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-0.9485</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.549</v>
+        <v>-0.5419</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8042</v>
+        <v>0.159</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9043</v>
+        <v>-0.2232</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1001</v>
+        <v>0.3823</v>
       </c>
       <c r="V8" t="n">
-        <v>0.9834000000000001</v>
+        <v>0.9805</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1093</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.6871</v>
+        <v>-2.0811</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2994</v>
+        <v>0.6278</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.9865</v>
+        <v>-2.7089</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.1701</v>
+        <v>-2.1695</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3594</v>
+        <v>0.3536</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.5295</v>
+        <v>-2.5231</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2218</v>
+        <v>1.1971</v>
       </c>
       <c r="K9" t="n">
-        <v>1.3365</v>
+        <v>1.3165</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.1147</v>
+        <v>-0.1194</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.392</v>
+        <v>-3.3667</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9771</v>
+        <v>-0.9629</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.4149</v>
+        <v>-2.4037</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.315</v>
+        <v>-0.7131</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6956</v>
+        <v>-0.3417</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6194</v>
+        <v>-0.3714</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1093</v>
+        <v>-0.1089</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1093</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.9316</v>
+        <v>-2.6293</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2609</v>
+        <v>0.6872</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.1925</v>
+        <v>-3.3166</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.8936</v>
+        <v>-1.8943</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3449</v>
+        <v>-0.3419</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.5487</v>
+        <v>-1.5523</v>
       </c>
       <c r="J10" t="n">
-        <v>1.8606</v>
+        <v>1.8316</v>
       </c>
       <c r="K10" t="n">
-        <v>1.309</v>
+        <v>1.296</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5516</v>
+        <v>0.5355</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.7542</v>
+        <v>-3.7258</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.6539</v>
+        <v>-1.638</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.1003</v>
+        <v>-2.0879</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5943000000000001</v>
+        <v>-0.2799</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9043</v>
+        <v>-0.4324</v>
       </c>
       <c r="U10" t="n">
-        <v>0.31</v>
+        <v>0.1524</v>
       </c>
       <c r="V10" t="n">
-        <v>1.1441</v>
+        <v>1.1383</v>
       </c>
       <c r="W10" t="n">
-        <v>1.7997</v>
+        <v>1.792</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.6556</v>
+        <v>-0.6536999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.8693</v>
+        <v>-4.9347</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.165</v>
+        <v>-3.4147</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.7043</v>
+        <v>-1.52</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.8017</v>
+        <v>-4.8051</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.3331</v>
+        <v>-3.3426</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.4687</v>
+        <v>-1.4625</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.2975</v>
+        <v>-2.3267</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.1828</v>
+        <v>-2.2073</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.1147</v>
+        <v>-0.1194</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.5043</v>
+        <v>-2.4784</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.1503</v>
+        <v>-1.1353</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.354</v>
+        <v>-1.3432</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3644</v>
+        <v>-0.4239</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2571</v>
+        <v>-0.4718</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1074</v>
+        <v>0.0479</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.6105</v>
+        <v>-0.6162</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.6105</v>
+        <v>-0.6162</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.9697</v>
+        <v>-5.923100000000002</v>
       </c>
       <c r="E12" t="n">
-        <v>7.591399999999999</v>
+        <v>8.375500000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-14.561</v>
+        <v>-14.2984</v>
       </c>
       <c r="G12" t="n">
-        <v>-7.090700000000001</v>
+        <v>-7.092500000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>0.07940000000000014</v>
+        <v>0.07209999999999983</v>
       </c>
       <c r="I12" t="n">
-        <v>-7.1702</v>
+        <v>-7.1647</v>
       </c>
       <c r="J12" t="n">
-        <v>16.2614</v>
+        <v>16.0482</v>
       </c>
       <c r="K12" t="n">
-        <v>9.691599999999999</v>
+        <v>9.5571</v>
       </c>
       <c r="L12" t="n">
-        <v>6.5697</v>
+        <v>6.491</v>
       </c>
       <c r="M12" t="n">
-        <v>-23.3522</v>
+        <v>-23.1407</v>
       </c>
       <c r="N12" t="n">
-        <v>-9.6121</v>
+        <v>-9.484999999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>-13.74</v>
+        <v>-13.656</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2685</v>
+        <v>2.2765</v>
       </c>
       <c r="Q12" t="n">
-        <v>-9.0733</v>
+        <v>-9.1051</v>
       </c>
       <c r="R12" t="n">
-        <v>11.3417</v>
+        <v>11.3817</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6047</v>
+        <v>0.4412</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.5858</v>
+        <v>-1.5354</v>
       </c>
       <c r="U12" t="n">
-        <v>1.981</v>
+        <v>1.9766</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.5426</v>
+        <v>-1.5478</v>
       </c>
       <c r="W12" t="n">
-        <v>2.9889</v>
+        <v>2.9678</v>
       </c>
       <c r="X12" t="n">
-        <v>-4.531499999999999</v>
+        <v>-4.5155</v>
       </c>
     </row>
     <row r="13">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.6889</v>
+        <v>3.2478</v>
       </c>
       <c r="E13" t="n">
-        <v>2.7105</v>
+        <v>3.154</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0216</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>2.4178</v>
+        <v>2.4185</v>
       </c>
       <c r="H13" t="n">
-        <v>0.44</v>
+        <v>0.4449</v>
       </c>
       <c r="I13" t="n">
-        <v>1.9778</v>
+        <v>1.9736</v>
       </c>
       <c r="J13" t="n">
-        <v>3.8963</v>
+        <v>3.88</v>
       </c>
       <c r="K13" t="n">
-        <v>1.2122</v>
+        <v>1.2066</v>
       </c>
       <c r="L13" t="n">
-        <v>2.6841</v>
+        <v>2.6734</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.4785</v>
+        <v>-1.4615</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.7721</v>
+        <v>-0.7617</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.7063</v>
+        <v>-0.6998</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2338</v>
+        <v>0.3333</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5565</v>
+        <v>-0.0838</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3227</v>
+        <v>0.4171</v>
       </c>
       <c r="V13" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="W13" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R. GIEDRAITIS</t>
+          <t>J. FERNANDEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.6373</v>
+        <v>2.6972</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5418</v>
+        <v>1.5692</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0954</v>
+        <v>1.128</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.1114</v>
+        <v>2.9353</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2538</v>
+        <v>1.6231</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3652</v>
+        <v>1.3123</v>
       </c>
       <c r="J14" t="n">
-        <v>1.8038</v>
+        <v>3.2188</v>
       </c>
       <c r="K14" t="n">
-        <v>1.2468</v>
+        <v>1.7819</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5570000000000001</v>
+        <v>1.4369</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.9152</v>
+        <v>-0.2835</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.993</v>
+        <v>-0.1588</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.9222</v>
+        <v>-0.1246</v>
       </c>
       <c r="P14" t="n">
-        <v>1.361</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R14" t="n">
-        <v>1.361</v>
+        <v>1.1382</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3876</v>
+        <v>-0.3959</v>
       </c>
       <c r="T14" t="n">
-        <v>0.738</v>
+        <v>-0.6692</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6496</v>
+        <v>0.2733</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ</t>
+          <t>R. GIEDRAITIS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.1298</v>
+        <v>1.8932</v>
       </c>
       <c r="E15" t="n">
-        <v>1.3762</v>
+        <v>1.7057</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7536</v>
+        <v>0.1875</v>
       </c>
       <c r="G15" t="n">
-        <v>2.9433</v>
+        <v>-0.0997</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6292</v>
+        <v>0.2637</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3141</v>
+        <v>-0.3634</v>
       </c>
       <c r="J15" t="n">
-        <v>3.254</v>
+        <v>1.7919</v>
       </c>
       <c r="K15" t="n">
-        <v>1.804</v>
+        <v>1.2411</v>
       </c>
       <c r="L15" t="n">
-        <v>1.4499</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.3107</v>
+        <v>-1.8916</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1749</v>
+        <v>-0.9774</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1359</v>
+        <v>-0.9143</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.3658</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1342</v>
+        <v>1.3658</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9742</v>
+        <v>0.6271</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9043</v>
+        <v>-0.0863</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0699</v>
+        <v>0.7134</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T. SCRUBB</t>
+          <t>M. HUERTAS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.7609</v>
+        <v>1.7412</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6795</v>
+        <v>4.1609</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.9185</v>
+        <v>-2.4197</v>
       </c>
       <c r="G16" t="n">
-        <v>1.2516</v>
+        <v>1.1267</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5266</v>
+        <v>-1.2089</v>
       </c>
       <c r="I16" t="n">
-        <v>0.725</v>
+        <v>2.3356</v>
       </c>
       <c r="J16" t="n">
-        <v>2.5887</v>
+        <v>3.9647</v>
       </c>
       <c r="K16" t="n">
-        <v>1.4719</v>
+        <v>-0.1314</v>
       </c>
       <c r="L16" t="n">
-        <v>1.1168</v>
+        <v>4.0961</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.3371</v>
+        <v>-2.838</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9453</v>
+        <v>-1.0775</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3918</v>
+        <v>-1.7604</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S16" t="n">
-        <v>1.1898</v>
+        <v>-0.3368</v>
       </c>
       <c r="T16" t="n">
-        <v>1.2249</v>
+        <v>-0.2998</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0351</v>
+        <v>-0.037</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.6342</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.6342</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. HUERTAS</t>
+          <t>A. DOORNEKAMP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5125</v>
+        <v>1.2655</v>
       </c>
       <c r="E17" t="n">
-        <v>4.0742</v>
+        <v>1.878</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.5617</v>
+        <v>-0.6125</v>
       </c>
       <c r="G17" t="n">
-        <v>1.1329</v>
+        <v>-0.2838</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.2048</v>
+        <v>-0.9540999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>2.3377</v>
+        <v>0.6703</v>
       </c>
       <c r="J17" t="n">
-        <v>3.9867</v>
+        <v>1.9526</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.1181</v>
+        <v>0.2101</v>
       </c>
       <c r="L17" t="n">
-        <v>4.1048</v>
+        <v>1.7425</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.8539</v>
+        <v>-2.2364</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.0867</v>
+        <v>-1.1642</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.7672</v>
+        <v>-1.0722</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.6805</v>
+        <v>1.1382</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4537</v>
+        <v>1.1382</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5789</v>
+        <v>0.4112</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4174</v>
+        <v>-0.0746</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1615</v>
+        <v>0.4857</v>
       </c>
       <c r="V17" t="n">
-        <v>1.639</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.639</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. DOORNEKAMP</t>
+          <t>T. SCRUBB</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.4249</v>
+        <v>0.6945</v>
       </c>
       <c r="E18" t="n">
-        <v>2.1295</v>
+        <v>1.7196</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7046</v>
+        <v>-1.0251</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2924</v>
+        <v>1.2566</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.9641</v>
+        <v>0.5311</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6717</v>
+        <v>0.7255</v>
       </c>
       <c r="J18" t="n">
-        <v>1.9692</v>
+        <v>2.5746</v>
       </c>
       <c r="K18" t="n">
-        <v>0.218</v>
+        <v>1.4651</v>
       </c>
       <c r="L18" t="n">
-        <v>1.7512</v>
+        <v>1.1094</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.2615</v>
+        <v>-1.318</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.1821</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.0795</v>
+        <v>-0.384</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1342</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1342</v>
+        <v>0.4553</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5831</v>
+        <v>0.1209</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1603</v>
+        <v>0.2832</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4228</v>
+        <v>-0.1623</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.84</v>
+        <v>0.6821</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7046</v>
+        <v>-0.4788</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5446</v>
+        <v>1.161</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.9816</v>
+        <v>-0.9735</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4431</v>
+        <v>-0.4342</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5384</v>
+        <v>-0.5393</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.1481</v>
+        <v>-0.1581</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1559</v>
+        <v>0.1551</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.3039</v>
+        <v>-0.3132</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8335</v>
+        <v>-0.8154</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.599</v>
+        <v>-0.5893</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2345</v>
+        <v>-0.226</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S19" t="n">
-        <v>0.143</v>
+        <v>-0.0289</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5565</v>
+        <v>-0.3207</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6995</v>
+        <v>0.2919</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="20">
@@ -1969,40 +1969,40 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4475</v>
+        <v>0.4527</v>
       </c>
       <c r="E20" t="n">
-        <v>1.7936</v>
+        <v>1.7894</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3461</v>
+        <v>-1.3367</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6083</v>
+        <v>0.6104000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.8471</v>
+        <v>-0.8418</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4554</v>
+        <v>1.4522</v>
       </c>
       <c r="J20" t="n">
-        <v>1.8632</v>
+        <v>1.8591</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="L20" t="n">
-        <v>1.8285</v>
+        <v>1.8246</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2549</v>
+        <v>-1.2487</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8817</v>
+        <v>-0.8763</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3732</v>
+        <v>-0.3724</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -2017,19 +2017,19 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0696</v>
+        <v>-0.0697</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0696</v>
+        <v>0.0697</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1568</v>
+        <v>0.0375</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8872</v>
+        <v>1.2091</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7305</v>
+        <v>-1.1715</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.1483</v>
+        <v>-1.1553</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.45</v>
+        <v>-0.4645</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6983</v>
+        <v>-0.6909</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4206</v>
+        <v>0.3916</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1967</v>
+        <v>0.1681</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2239</v>
+        <v>0.2234</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.5689</v>
+        <v>-1.5469</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.9222</v>
+        <v>-0.9143</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3977</v>
+        <v>0.2823</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6261</v>
+        <v>-0.272</v>
       </c>
       <c r="U21" t="n">
-        <v>1.0238</v>
+        <v>0.5543</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4514</v>
+        <v>-2.1582</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.641</v>
+        <v>-0.4366</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.8104</v>
+        <v>-1.7216</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3431</v>
+        <v>0.3398</v>
       </c>
       <c r="H22" t="n">
-        <v>0.511</v>
+        <v>0.5003</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1679</v>
+        <v>-0.1606</v>
       </c>
       <c r="J22" t="n">
-        <v>2.1838</v>
+        <v>2.1605</v>
       </c>
       <c r="K22" t="n">
-        <v>1.9599</v>
+        <v>1.937</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2239</v>
+        <v>0.2234</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.8407</v>
+        <v>-1.8207</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.4489</v>
+        <v>-1.4367</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.3918</v>
+        <v>-0.384</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4996</v>
+        <v>-0.202</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5565</v>
+        <v>-0.3207</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0569</v>
+        <v>0.1187</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.1775</v>
+        <v>-3.5849</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.2858</v>
+        <v>-1.972</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.8916</v>
+        <v>-1.613</v>
       </c>
       <c r="G23" t="n">
-        <v>0.9274</v>
+        <v>0.9177</v>
       </c>
       <c r="H23" t="n">
-        <v>0.469</v>
+        <v>0.4682</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4584</v>
+        <v>0.4495</v>
       </c>
       <c r="J23" t="n">
-        <v>1.534</v>
+        <v>1.5054</v>
       </c>
       <c r="K23" t="n">
-        <v>1.4302</v>
+        <v>1.4167</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1038</v>
+        <v>0.0887</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.6066</v>
+        <v>-0.5877</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-0.9485</v>
       </c>
       <c r="O23" t="n">
-        <v>0.3546</v>
+        <v>0.3608</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8099</v>
+        <v>-0.2067</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4174</v>
+        <v>-0.0629</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3926</v>
+        <v>-0.1438</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>6.9697</v>
+        <v>6.968599999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>14.5611</v>
+        <v>14.2985</v>
       </c>
       <c r="F24" t="n">
-        <v>-7.5914</v>
+        <v>-7.329800000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>7.0907</v>
+        <v>7.092700000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.07949999999999968</v>
+        <v>-0.07219999999999976</v>
       </c>
       <c r="I24" t="n">
-        <v>7.1703</v>
+        <v>7.1648</v>
       </c>
       <c r="J24" t="n">
-        <v>23.3522</v>
+        <v>23.1411</v>
       </c>
       <c r="K24" t="n">
-        <v>9.612099999999998</v>
+        <v>9.4848</v>
       </c>
       <c r="L24" t="n">
-        <v>13.74</v>
+        <v>13.6561</v>
       </c>
       <c r="M24" t="n">
-        <v>-16.2615</v>
+        <v>-16.0484</v>
       </c>
       <c r="N24" t="n">
-        <v>-9.691599999999999</v>
+        <v>-9.556999999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>-6.57</v>
+        <v>-6.4912</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.2684</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q24" t="n">
-        <v>-11.3417</v>
+        <v>-11.3817</v>
       </c>
       <c r="R24" t="n">
-        <v>9.073399999999999</v>
+        <v>9.105399999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>0.6047999999999999</v>
+        <v>0.6044999999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.9811</v>
+        <v>-1.9765</v>
       </c>
       <c r="U24" t="n">
-        <v>2.5858</v>
+        <v>2.581</v>
       </c>
       <c r="V24" t="n">
-        <v>1.542400000000001</v>
+        <v>1.5478</v>
       </c>
       <c r="W24" t="n">
-        <v>4.5314</v>
+        <v>4.5157</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.989</v>
+        <v>-2.9679</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104611_W17.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104611_W17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104611_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104611_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104611_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-2.2879</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104611_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104611_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104611_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104611_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104611_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.6536999999999999</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104611_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104611_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-4.5155</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>0</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104611_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104611_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104611_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104611_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104611_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104611_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104611_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104611_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104611_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104611_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104611_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,7 @@
       <c r="X24" t="n">
         <v>-2.9679</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
